--- a/icfd2026/paper/figures/lbv_num_phi-10.xlsx
+++ b/icfd2026/paper/figures/lbv_num_phi-10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\arr\lab\presentations\icfd2026\paper\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58A60D71-F913-41B1-BBF9-E33C149E947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9055CBBA-C438-45DF-9D1E-04248CA1FBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12030" yWindow="4065" windowWidth="13260" windowHeight="9270" xr2:uid="{8A2922A7-97E9-46A4-AC71-0CE1B71449A3}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" xr2:uid="{8A2922A7-97E9-46A4-AC71-0CE1B71449A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,10 +47,10 @@
     <t>Present Mech</t>
   </si>
   <si>
-    <t>Gotama 2022</t>
+    <t>Gotama Detailed 2022</t>
   </si>
   <si>
-    <t>Okafor Reduced (2019)</t>
+    <t>Okafor Reduced 2019</t>
   </si>
 </sst>
 </file>
